--- a/excel/Mobile_E2E_Report.xlsx
+++ b/excel/Mobile_E2E_Report.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="773" uniqueCount="261">
   <si>
     <t>Metric</t>
   </si>
@@ -25,7 +25,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>12/6/2026</t>
+    <t>16/6/2026</t>
   </si>
   <si>
     <t>Device Name</t>
@@ -55,13 +55,13 @@
     <t>Pass Percentage</t>
   </si>
   <si>
-    <t>0.0%</t>
+    <t>100.0%</t>
   </si>
   <si>
     <t>Execution Duration</t>
   </si>
   <si>
-    <t>26329.27s</t>
+    <t>1089.99s</t>
   </si>
   <si>
     <t>Test ID</t>
@@ -88,6 +88,432 @@
     <t>Duration</t>
   </si>
   <si>
+    <t>TC</t>
+  </si>
+  <si>
+    <t>AdminPanel</t>
+  </si>
+  <si>
+    <t>TC_901_Verify_Admin_Panel_Navigation_And_Data_Display</t>
+  </si>
+  <si>
+    <t>11:54:34 pm</t>
+  </si>
+  <si>
+    <t>11:54:45 pm</t>
+  </si>
+  <si>
+    <t>10.60s</t>
+  </si>
+  <si>
+    <t>Authentication</t>
+  </si>
+  <si>
+    <t>TC_001_Verify_Login_Validation_Empty_Fields</t>
+  </si>
+  <si>
+    <t>11:56:05 pm</t>
+  </si>
+  <si>
+    <t>11:56:22 pm</t>
+  </si>
+  <si>
+    <t>17.64s</t>
+  </si>
+  <si>
+    <t>TC_002_Verify_Login_Validation_Invalid_Format</t>
+  </si>
+  <si>
+    <t>11:56:38 pm</t>
+  </si>
+  <si>
+    <t>15.89s</t>
+  </si>
+  <si>
+    <t>TC_003_Verify_OTP_Login_Bypass</t>
+  </si>
+  <si>
+    <t>11:56:50 pm</t>
+  </si>
+  <si>
+    <t>11.87s</t>
+  </si>
+  <si>
+    <t>TC_004_Verify_Logout_Functionality</t>
+  </si>
+  <si>
+    <t>11:57:02 pm</t>
+  </si>
+  <si>
+    <t>11.54s</t>
+  </si>
+  <si>
+    <t>TC_011_Verify_Sign_Up_Mode_Toggle</t>
+  </si>
+  <si>
+    <t>11:57:20 pm</t>
+  </si>
+  <si>
+    <t>18.74s</t>
+  </si>
+  <si>
+    <t>TC_012_Verify_Sign_Up_Validation_Empty_Fields</t>
+  </si>
+  <si>
+    <t>11:57:28 pm</t>
+  </si>
+  <si>
+    <t>7.31s</t>
+  </si>
+  <si>
+    <t>TC_013_Verify_Sign_Up_Successful</t>
+  </si>
+  <si>
+    <t>11:57:37 pm</t>
+  </si>
+  <si>
+    <t>9.45s</t>
+  </si>
+  <si>
+    <t>TC_014_Verify_Forgot_Password_Validation_Empty_Email</t>
+  </si>
+  <si>
+    <t>11:57:53 pm</t>
+  </si>
+  <si>
+    <t>15.76s</t>
+  </si>
+  <si>
+    <t>TC_015_Verify_Forgot_Password_Success</t>
+  </si>
+  <si>
+    <t>11:58:33 pm</t>
+  </si>
+  <si>
+    <t>39.98s</t>
+  </si>
+  <si>
+    <t>CallDetection</t>
+  </si>
+  <si>
+    <t>TC_401_Verify_Custom_Number_Analysis_Empty_Input</t>
+  </si>
+  <si>
+    <t>11:59:13 pm</t>
+  </si>
+  <si>
+    <t>11:59:30 pm</t>
+  </si>
+  <si>
+    <t>17.58s</t>
+  </si>
+  <si>
+    <t>TC_402_Verify_Custom_Number_Analysis_Valid_Input</t>
+  </si>
+  <si>
+    <t>11:59:40 pm</t>
+  </si>
+  <si>
+    <t>9.16s</t>
+  </si>
+  <si>
+    <t>TC_403_Verify_Lottery_Prize_Scam_Preset</t>
+  </si>
+  <si>
+    <t>12:00:11 am</t>
+  </si>
+  <si>
+    <t>31.89s</t>
+  </si>
+  <si>
+    <t>TC_404_Verify_Police_Threat_Scam_Preset</t>
+  </si>
+  <si>
+    <t>12:00:16 am</t>
+  </si>
+  <si>
+    <t>4.72s</t>
+  </si>
+  <si>
+    <t>TC_405_Verify_Normal_Friend_Call_Preset</t>
+  </si>
+  <si>
+    <t>12:00:39 am</t>
+  </si>
+  <si>
+    <t>22.42s</t>
+  </si>
+  <si>
+    <t>TC_406_Verify_Active_Call_Hangup</t>
+  </si>
+  <si>
+    <t>12:00:53 am</t>
+  </si>
+  <si>
+    <t>14.38s</t>
+  </si>
+  <si>
+    <t>Chatbot</t>
+  </si>
+  <si>
+    <t>TC_601_Verify_Chatbot_Empty_Query_Submission</t>
+  </si>
+  <si>
+    <t>12:01:15 am</t>
+  </si>
+  <si>
+    <t>12:01:26 am</t>
+  </si>
+  <si>
+    <t>11.11s</t>
+  </si>
+  <si>
+    <t>TC_602_Verify_Chatbot_Successful_Query</t>
+  </si>
+  <si>
+    <t>12:01:37 am</t>
+  </si>
+  <si>
+    <t>11.27s</t>
+  </si>
+  <si>
+    <t>TC_603_Verify_Chatbot_Multi_Turn_Conversation</t>
+  </si>
+  <si>
+    <t>12:01:56 am</t>
+  </si>
+  <si>
+    <t>18.36s</t>
+  </si>
+  <si>
+    <t>EndToEndFlow</t>
+  </si>
+  <si>
+    <t>TC_301_Execute_Complete_Banking_Safety_Workflow</t>
+  </si>
+  <si>
+    <t>12:02:17 am</t>
+  </si>
+  <si>
+    <t>12:03:00 am</t>
+  </si>
+  <si>
+    <t>42.05s</t>
+  </si>
+  <si>
+    <t>TC_303_Execute_Settings_Accessibility_And_Profile_Workflow</t>
+  </si>
+  <si>
+    <t>12:04:40 am</t>
+  </si>
+  <si>
+    <t>100.95s</t>
+  </si>
+  <si>
+    <t>FormValidation</t>
+  </si>
+  <si>
+    <t>TC_101_Verify_Report_Fraud_Empty_Submission_Validation</t>
+  </si>
+  <si>
+    <t>12:05:18 am</t>
+  </si>
+  <si>
+    <t>12:05:28 am</t>
+  </si>
+  <si>
+    <t>10.63s</t>
+  </si>
+  <si>
+    <t>TC_102_Verify_Report_Fraud_Successful_Submission</t>
+  </si>
+  <si>
+    <t>12:05:34 am</t>
+  </si>
+  <si>
+    <t>5.81s</t>
+  </si>
+  <si>
+    <t>TC_103_Verify_Report_Fraud_Validation_Empty_Details</t>
+  </si>
+  <si>
+    <t>12:06:01 am</t>
+  </si>
+  <si>
+    <t>27.31s</t>
+  </si>
+  <si>
+    <t>TC_104_Verify_Report_Fraud_Validation_Empty_Target</t>
+  </si>
+  <si>
+    <t>12:07:02 am</t>
+  </si>
+  <si>
+    <t>60.78s</t>
+  </si>
+  <si>
+    <t>Gestures</t>
+  </si>
+  <si>
+    <t>TC_201_Verify_Dashboard_List_Scrolling</t>
+  </si>
+  <si>
+    <t>12:07:26 am</t>
+  </si>
+  <si>
+    <t>12:07:42 am</t>
+  </si>
+  <si>
+    <t>15.69s</t>
+  </si>
+  <si>
+    <t>TC_202_Verify_Scroll_Until_Visible_In_Learning_Hub</t>
+  </si>
+  <si>
+    <t>12:07:44 am</t>
+  </si>
+  <si>
+    <t>1.52s</t>
+  </si>
+  <si>
+    <t>TC_203_Verify_Tutorials_Back_Navigation</t>
+  </si>
+  <si>
+    <t>12:07:50 am</t>
+  </si>
+  <si>
+    <t>6.24s</t>
+  </si>
+  <si>
+    <t>Settings</t>
+  </si>
+  <si>
+    <t>TC_801_Verify_Language_Change_Telugu</t>
+  </si>
+  <si>
+    <t>12:08:13 am</t>
+  </si>
+  <si>
+    <t>12:08:17 am</t>
+  </si>
+  <si>
+    <t>4.21s</t>
+  </si>
+  <si>
+    <t>TC_802_Verify_Language_Change_Hindi</t>
+  </si>
+  <si>
+    <t>12:08:22 am</t>
+  </si>
+  <si>
+    <t>4.43s</t>
+  </si>
+  <si>
+    <t>TC_803_Verify_Language_Change_Tamil</t>
+  </si>
+  <si>
+    <t>12:08:30 am</t>
+  </si>
+  <si>
+    <t>8.74s</t>
+  </si>
+  <si>
+    <t>TC_804_Verify_Toggle_Voice_Navigation_Switch</t>
+  </si>
+  <si>
+    <t>12:08:52 am</t>
+  </si>
+  <si>
+    <t>21.57s</t>
+  </si>
+  <si>
+    <t>TC_805_Verify_Toggle_High_Contrast_Switch</t>
+  </si>
+  <si>
+    <t>12:09:23 am</t>
+  </si>
+  <si>
+    <t>30.81s</t>
+  </si>
+  <si>
+    <t>TC_806_Verify_Settings_Navigation_From_Dashboard</t>
+  </si>
+  <si>
+    <t>12:09:35 am</t>
+  </si>
+  <si>
+    <t>11.95s</t>
+  </si>
+  <si>
+    <t>TC_807_Verify_Text_Scale_Large</t>
+  </si>
+  <si>
+    <t>12:09:55 am</t>
+  </si>
+  <si>
+    <t>20.34s</t>
+  </si>
+  <si>
+    <t>TC_808_Verify_Text_Scale_Extra_Large</t>
+  </si>
+  <si>
+    <t>12:10:40 am</t>
+  </si>
+  <si>
+    <t>45.15s</t>
+  </si>
+  <si>
+    <t>SmsScanning</t>
+  </si>
+  <si>
+    <t>TC_501_Verify_Sms_Scan_Empty_Input</t>
+  </si>
+  <si>
+    <t>12:11:04 am</t>
+  </si>
+  <si>
+    <t>12:11:52 am</t>
+  </si>
+  <si>
+    <t>47.78s</t>
+  </si>
+  <si>
+    <t>TC_502_Verify_Sms_Scan_Fraud_Message</t>
+  </si>
+  <si>
+    <t>12:12:05 am</t>
+  </si>
+  <si>
+    <t>12.84s</t>
+  </si>
+  <si>
+    <t>TC_503_Verify_Sms_Scan_Safe_Message</t>
+  </si>
+  <si>
+    <t>12:12:09 am</t>
+  </si>
+  <si>
+    <t>3.93s</t>
+  </si>
+  <si>
+    <t>TC_504_Verify_Sms_Scan_UPI_Scam</t>
+  </si>
+  <si>
+    <t>12:12:12 am</t>
+  </si>
+  <si>
+    <t>3.00s</t>
+  </si>
+  <si>
+    <t>TC_505_Verify_Sms_Scan_Card_Block_Scam</t>
+  </si>
+  <si>
+    <t>12:12:17 am</t>
+  </si>
+  <si>
+    <t>4.96s</t>
+  </si>
+  <si>
     <t>Test Name</t>
   </si>
   <si>
@@ -110,13 +536,274 @@
   </si>
   <si>
     <t>Remarks</t>
+  </si>
+  <si>
+    <t>2026-06-15T18:24:34.784Z</t>
+  </si>
+  <si>
+    <t>Test Suite Init</t>
+  </si>
+  <si>
+    <t>SUCCESS</t>
+  </si>
+  <si>
+    <t>Starting scenario in module: AdminPanel</t>
+  </si>
+  <si>
+    <t>2026-06-15T18:24:45.391Z</t>
+  </si>
+  <si>
+    <t>Test Suite Teardown</t>
+  </si>
+  <si>
+    <t>PASS</t>
+  </si>
+  <si>
+    <t>Scenario completed with no errors.</t>
+  </si>
+  <si>
+    <t>2026-06-15T18:26:05.189Z</t>
+  </si>
+  <si>
+    <t>Starting scenario in module: Authentication</t>
+  </si>
+  <si>
+    <t>2026-06-15T18:26:22.824Z</t>
+  </si>
+  <si>
+    <t>2026-06-15T18:26:22.828Z</t>
+  </si>
+  <si>
+    <t>2026-06-15T18:26:38.721Z</t>
+  </si>
+  <si>
+    <t>2026-06-15T18:26:50.591Z</t>
+  </si>
+  <si>
+    <t>2026-06-15T18:26:50.592Z</t>
+  </si>
+  <si>
+    <t>2026-06-15T18:27:02.132Z</t>
+  </si>
+  <si>
+    <t>2026-06-15T18:27:02.136Z</t>
+  </si>
+  <si>
+    <t>2026-06-15T18:27:20.872Z</t>
+  </si>
+  <si>
+    <t>2026-06-15T18:27:20.873Z</t>
+  </si>
+  <si>
+    <t>2026-06-15T18:27:28.183Z</t>
+  </si>
+  <si>
+    <t>2026-06-15T18:27:28.185Z</t>
+  </si>
+  <si>
+    <t>2026-06-15T18:27:37.633Z</t>
+  </si>
+  <si>
+    <t>2026-06-15T18:27:53.392Z</t>
+  </si>
+  <si>
+    <t>2026-06-15T18:27:53.393Z</t>
+  </si>
+  <si>
+    <t>2026-06-15T18:28:33.378Z</t>
+  </si>
+  <si>
+    <t>2026-06-15T18:29:13.293Z</t>
+  </si>
+  <si>
+    <t>Starting scenario in module: CallDetection</t>
+  </si>
+  <si>
+    <t>2026-06-15T18:29:30.871Z</t>
+  </si>
+  <si>
+    <t>2026-06-15T18:29:30.875Z</t>
+  </si>
+  <si>
+    <t>2026-06-15T18:29:40.030Z</t>
+  </si>
+  <si>
+    <t>2026-06-15T18:29:40.031Z</t>
+  </si>
+  <si>
+    <t>2026-06-15T18:30:11.922Z</t>
+  </si>
+  <si>
+    <t>2026-06-15T18:30:11.923Z</t>
+  </si>
+  <si>
+    <t>2026-06-15T18:30:16.642Z</t>
+  </si>
+  <si>
+    <t>2026-06-15T18:30:39.062Z</t>
+  </si>
+  <si>
+    <t>2026-06-15T18:30:53.440Z</t>
+  </si>
+  <si>
+    <t>2026-06-15T18:31:15.367Z</t>
+  </si>
+  <si>
+    <t>Starting scenario in module: Chatbot</t>
+  </si>
+  <si>
+    <t>2026-06-15T18:31:26.477Z</t>
+  </si>
+  <si>
+    <t>2026-06-15T18:31:37.743Z</t>
+  </si>
+  <si>
+    <t>2026-06-15T18:31:56.104Z</t>
+  </si>
+  <si>
+    <t>2026-06-15T18:32:17.948Z</t>
+  </si>
+  <si>
+    <t>Starting scenario in module: EndToEndFlow</t>
+  </si>
+  <si>
+    <t>2026-06-15T18:33:00.006Z</t>
+  </si>
+  <si>
+    <t>2026-06-15T18:33:00.007Z</t>
+  </si>
+  <si>
+    <t>2026-06-15T18:34:40.959Z</t>
+  </si>
+  <si>
+    <t>2026-06-15T18:35:18.106Z</t>
+  </si>
+  <si>
+    <t>Starting scenario in module: FormValidation</t>
+  </si>
+  <si>
+    <t>2026-06-15T18:35:28.737Z</t>
+  </si>
+  <si>
+    <t>2026-06-15T18:35:28.738Z</t>
+  </si>
+  <si>
+    <t>2026-06-15T18:35:34.548Z</t>
+  </si>
+  <si>
+    <t>2026-06-15T18:36:01.857Z</t>
+  </si>
+  <si>
+    <t>2026-06-15T18:37:02.637Z</t>
+  </si>
+  <si>
+    <t>2026-06-15T18:37:26.955Z</t>
+  </si>
+  <si>
+    <t>Starting scenario in module: Gestures</t>
+  </si>
+  <si>
+    <t>2026-06-15T18:37:42.644Z</t>
+  </si>
+  <si>
+    <t>2026-06-15T18:37:42.645Z</t>
+  </si>
+  <si>
+    <t>2026-06-15T18:37:44.162Z</t>
+  </si>
+  <si>
+    <t>2026-06-15T18:37:44.163Z</t>
+  </si>
+  <si>
+    <t>2026-06-15T18:37:50.399Z</t>
+  </si>
+  <si>
+    <t>2026-06-15T18:38:13.430Z</t>
+  </si>
+  <si>
+    <t>Starting scenario in module: Settings</t>
+  </si>
+  <si>
+    <t>2026-06-15T18:38:17.643Z</t>
+  </si>
+  <si>
+    <t>2026-06-15T18:38:17.645Z</t>
+  </si>
+  <si>
+    <t>2026-06-15T18:38:22.080Z</t>
+  </si>
+  <si>
+    <t>2026-06-15T18:38:30.819Z</t>
+  </si>
+  <si>
+    <t>2026-06-15T18:38:30.821Z</t>
+  </si>
+  <si>
+    <t>2026-06-15T18:38:52.387Z</t>
+  </si>
+  <si>
+    <t>2026-06-15T18:38:52.388Z</t>
+  </si>
+  <si>
+    <t>2026-06-15T18:39:23.196Z</t>
+  </si>
+  <si>
+    <t>2026-06-15T18:39:23.197Z</t>
+  </si>
+  <si>
+    <t>2026-06-15T18:39:35.145Z</t>
+  </si>
+  <si>
+    <t>2026-06-15T18:39:35.146Z</t>
+  </si>
+  <si>
+    <t>2026-06-15T18:39:55.482Z</t>
+  </si>
+  <si>
+    <t>2026-06-15T18:39:55.484Z</t>
+  </si>
+  <si>
+    <t>2026-06-15T18:40:40.637Z</t>
+  </si>
+  <si>
+    <t>2026-06-15T18:41:04.954Z</t>
+  </si>
+  <si>
+    <t>Starting scenario in module: SmsScanning</t>
+  </si>
+  <si>
+    <t>2026-06-15T18:41:52.738Z</t>
+  </si>
+  <si>
+    <t>2026-06-15T18:41:52.740Z</t>
+  </si>
+  <si>
+    <t>2026-06-15T18:42:05.575Z</t>
+  </si>
+  <si>
+    <t>2026-06-15T18:42:05.576Z</t>
+  </si>
+  <si>
+    <t>2026-06-15T18:42:09.505Z</t>
+  </si>
+  <si>
+    <t>2026-06-15T18:42:09.506Z</t>
+  </si>
+  <si>
+    <t>2026-06-15T18:42:12.503Z</t>
+  </si>
+  <si>
+    <t>2026-06-15T18:42:12.504Z</t>
+  </si>
+  <si>
+    <t>2026-06-15T18:42:17.467Z</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -140,11 +827,23 @@
     </font>
     <font>
       <b/>
+      <color rgb="2E7D32"/>
+    </font>
+    <font>
+      <b/>
     </font>
     <font>
       <b/>
       <color rgb="FFFFFF"/>
       <sz val="11"/>
+      <name val="Segoe UI"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Segoe UI"/>
+    </font>
+    <font>
+      <sz val="9"/>
       <name val="Segoe UI"/>
     </font>
   </fonts>
@@ -193,7 +892,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -207,13 +906,25 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -599,15 +1310,15 @@
         <v>8</v>
       </c>
       <c r="B5" s="2">
-        <v>0</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="2">
-        <v>0</v>
+      <c r="B6" s="4">
+        <v>41</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -630,7 +1341,7 @@
       <c r="A9" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="5" t="s">
         <v>13</v>
       </c>
     </row>
@@ -650,7 +1361,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H42"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -662,30 +1373,1096 @@
     <col min="8" max="8" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+    <row r="1" ht="26" customHeight="1" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="6" t="s">
         <v>23</v>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="H2" s="7" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="H4" s="7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="H10" s="7" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="H11" s="7" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="H12" s="7" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="H13" s="7" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="H14" s="7" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="H15" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="G16" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H16" s="7" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="G17" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="H17" s="7" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="G18" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="H18" s="7" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F19" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="G19" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="H19" s="7" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="20" ht="22" customHeight="1" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="G20" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="H20" s="7" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F21" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="G21" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="H21" s="7" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="22" ht="22" customHeight="1" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F22" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="G22" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="H22" s="7" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="23" ht="22" customHeight="1" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F23" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="G23" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="H23" s="7" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="24" ht="22" customHeight="1" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F24" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="G24" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="H24" s="7" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="25" ht="22" customHeight="1" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F25" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="G25" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="H25" s="7" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="26" ht="22" customHeight="1" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F26" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="G26" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="H26" s="7" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="27" ht="22" customHeight="1" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F27" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G27" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="H27" s="7" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="28" ht="22" customHeight="1" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F28" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="G28" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="H28" s="7" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="29" ht="22" customHeight="1" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F29" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="G29" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="H29" s="7" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="30" ht="22" customHeight="1" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F30" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="G30" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="H30" s="7" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="31" ht="22" customHeight="1" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F31" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="G31" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="H31" s="7" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="32" ht="22" customHeight="1" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F32" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="G32" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="H32" s="7" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="33" ht="22" customHeight="1" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F33" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="G33" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="H33" s="7" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="34" ht="22" customHeight="1" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="C34" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="D34" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F34" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="G34" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="H34" s="7" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="35" ht="22" customHeight="1" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F35" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="G35" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="H35" s="7" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="36" ht="22" customHeight="1" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B36" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="C36" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="D36" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E36" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F36" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="G36" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="H36" s="7" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="37" ht="22" customHeight="1" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F37" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="G37" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="H37" s="7" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="38" ht="22" customHeight="1" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B38" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="C38" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="D38" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E38" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F38" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="G38" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="H38" s="7" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="39" ht="22" customHeight="1" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B39" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="C39" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="D39" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F39" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G39" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="H39" s="7" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="40" ht="22" customHeight="1" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B40" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="C40" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="D40" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E40" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F40" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="G40" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="H40" s="7" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="41" ht="22" customHeight="1" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B41" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="C41" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E41" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F41" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="G41" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="H41" s="7" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="42" ht="22" customHeight="1" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B42" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="C42" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="D42" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E42" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F42" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="G42" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="H42" s="7" t="s">
+        <v>165</v>
       </c>
     </row>
   </sheetData>
@@ -707,24 +2484,24 @@
     <col min="6" max="6" width="25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="D1" s="6" t="s">
+    <row r="1" ht="26" customHeight="1" spans="1:6" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="D1" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="F1" s="6" t="s">
-        <v>27</v>
+      <c r="F1" s="8" t="s">
+        <v>169</v>
       </c>
     </row>
   </sheetData>
@@ -735,7 +2512,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E83"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -745,21 +2522,1415 @@
     <col min="5" max="5" width="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1" spans="1:5" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="B1" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C1" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="D1" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="E1" s="7" t="s">
+    <row r="1" ht="26" customHeight="1" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="E2" s="10" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="B4" s="10" t="s">
         <v>31</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="10" t="s">
+        <v>185</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="E8" s="10" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="E10" s="10" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="E11" s="10" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="10" t="s">
+        <v>190</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="10" t="s">
+        <v>191</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="E13" s="10" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="10" t="s">
+        <v>192</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="E14" s="10" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="E15" s="10" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="D16" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="E16" s="10" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="17" ht="20" customHeight="1" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="10" t="s">
+        <v>195</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="D17" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="E17" s="10" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="10" t="s">
+        <v>195</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="C18" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="D18" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="E18" s="10" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="19" ht="20" customHeight="1" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="D19" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="E19" s="10" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="20" ht="20" customHeight="1" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="B20" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="C20" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="D20" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="E20" s="10" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="10" t="s">
+        <v>198</v>
+      </c>
+      <c r="B21" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="C21" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="D21" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="E21" s="10" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="22" ht="20" customHeight="1" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="10" t="s">
+        <v>199</v>
+      </c>
+      <c r="B22" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="C22" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="D22" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="E22" s="10" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="23" ht="20" customHeight="1" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="10" t="s">
+        <v>201</v>
+      </c>
+      <c r="B23" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="C23" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="D23" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="E23" s="10" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="24" ht="20" customHeight="1" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="B24" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="C24" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="D24" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="E24" s="10" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="25" ht="20" customHeight="1" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="10" t="s">
+        <v>203</v>
+      </c>
+      <c r="B25" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="C25" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="D25" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="E25" s="10" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="26" ht="20" customHeight="1" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="10" t="s">
+        <v>204</v>
+      </c>
+      <c r="B26" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="C26" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="D26" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="E26" s="10" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="27" ht="20" customHeight="1" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="10" t="s">
+        <v>205</v>
+      </c>
+      <c r="B27" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="C27" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="D27" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="E27" s="10" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="28" ht="20" customHeight="1" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="B28" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="C28" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="D28" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="E28" s="10" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="29" ht="20" customHeight="1" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="B29" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="C29" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="D29" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="E29" s="10" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="30" ht="20" customHeight="1" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="B30" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C30" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="D30" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="E30" s="10" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="31" ht="20" customHeight="1" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="B31" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C31" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="D31" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="E31" s="10" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="32" ht="20" customHeight="1" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="B32" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="C32" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="D32" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="E32" s="10" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="33" ht="20" customHeight="1" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="B33" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="C33" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="D33" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="E33" s="10" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="34" ht="20" customHeight="1" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="10" t="s">
+        <v>210</v>
+      </c>
+      <c r="B34" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="C34" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="D34" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="E34" s="10" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="35" ht="20" customHeight="1" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="10" t="s">
+        <v>212</v>
+      </c>
+      <c r="B35" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="C35" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="D35" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="E35" s="10" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="36" ht="20" customHeight="1" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="10" t="s">
+        <v>212</v>
+      </c>
+      <c r="B36" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="C36" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="D36" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="E36" s="10" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="37" ht="20" customHeight="1" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="10" t="s">
+        <v>213</v>
+      </c>
+      <c r="B37" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="C37" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="D37" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="E37" s="10" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="38" ht="20" customHeight="1" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="10" t="s">
+        <v>213</v>
+      </c>
+      <c r="B38" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="C38" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="D38" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="E38" s="10" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="39" ht="20" customHeight="1" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="10" t="s">
+        <v>214</v>
+      </c>
+      <c r="B39" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="C39" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="D39" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="E39" s="10" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="40" ht="20" customHeight="1" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="10" t="s">
+        <v>215</v>
+      </c>
+      <c r="B40" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="C40" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="D40" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="E40" s="10" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="41" ht="20" customHeight="1" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="10" t="s">
+        <v>217</v>
+      </c>
+      <c r="B41" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="C41" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="D41" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="E41" s="10" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="42" ht="20" customHeight="1" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="B42" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="C42" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="D42" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="E42" s="10" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="43" ht="20" customHeight="1" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="10" t="s">
+        <v>219</v>
+      </c>
+      <c r="B43" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="C43" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="D43" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="E43" s="10" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="44" ht="20" customHeight="1" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="B44" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="C44" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="D44" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="E44" s="10" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="45" ht="20" customHeight="1" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="10" t="s">
+        <v>222</v>
+      </c>
+      <c r="B45" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="C45" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="D45" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="E45" s="10" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="46" ht="20" customHeight="1" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="10" t="s">
+        <v>223</v>
+      </c>
+      <c r="B46" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="C46" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="D46" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="E46" s="10" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="47" ht="20" customHeight="1" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="10" t="s">
+        <v>224</v>
+      </c>
+      <c r="B47" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="C47" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="D47" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="E47" s="10" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="48" ht="20" customHeight="1" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="10" t="s">
+        <v>224</v>
+      </c>
+      <c r="B48" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="C48" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="D48" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="E48" s="10" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="49" ht="20" customHeight="1" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="10" t="s">
+        <v>225</v>
+      </c>
+      <c r="B49" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="C49" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="D49" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="E49" s="10" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="50" ht="20" customHeight="1" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="10" t="s">
+        <v>225</v>
+      </c>
+      <c r="B50" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="C50" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="D50" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="E50" s="10" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="51" ht="20" customHeight="1" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="10" t="s">
+        <v>226</v>
+      </c>
+      <c r="B51" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="C51" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="D51" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="E51" s="10" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="52" ht="20" customHeight="1" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="10" t="s">
+        <v>227</v>
+      </c>
+      <c r="B52" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="C52" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="D52" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="E52" s="10" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="53" ht="20" customHeight="1" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="B53" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="C53" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="D53" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="E53" s="10" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="54" ht="20" customHeight="1" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="10" t="s">
+        <v>230</v>
+      </c>
+      <c r="B54" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="C54" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="D54" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="E54" s="10" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="55" ht="20" customHeight="1" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="B55" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="C55" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="D55" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="E55" s="10" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="56" ht="20" customHeight="1" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="10" t="s">
+        <v>232</v>
+      </c>
+      <c r="B56" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="C56" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="D56" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="E56" s="10" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="57" ht="20" customHeight="1" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="10" t="s">
+        <v>233</v>
+      </c>
+      <c r="B57" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="C57" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="D57" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="E57" s="10" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="58" ht="20" customHeight="1" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="10" t="s">
+        <v>234</v>
+      </c>
+      <c r="B58" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="C58" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="D58" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="E58" s="10" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="59" ht="20" customHeight="1" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="10" t="s">
+        <v>236</v>
+      </c>
+      <c r="B59" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="C59" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="D59" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="E59" s="10" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="60" ht="20" customHeight="1" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="10" t="s">
+        <v>237</v>
+      </c>
+      <c r="B60" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="C60" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="D60" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="E60" s="10" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="61" ht="20" customHeight="1" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="10" t="s">
+        <v>238</v>
+      </c>
+      <c r="B61" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="C61" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="D61" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="E61" s="10" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="62" ht="20" customHeight="1" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="10" t="s">
+        <v>238</v>
+      </c>
+      <c r="B62" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C62" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="D62" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="E62" s="10" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="63" ht="20" customHeight="1" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="10" t="s">
+        <v>239</v>
+      </c>
+      <c r="B63" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C63" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="D63" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="E63" s="10" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="64" ht="20" customHeight="1" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="10" t="s">
+        <v>240</v>
+      </c>
+      <c r="B64" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="C64" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="D64" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="E64" s="10" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="65" ht="20" customHeight="1" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="10" t="s">
+        <v>241</v>
+      </c>
+      <c r="B65" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="C65" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="D65" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="E65" s="10" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="66" ht="20" customHeight="1" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="10" t="s">
+        <v>242</v>
+      </c>
+      <c r="B66" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="C66" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="D66" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="E66" s="10" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="67" ht="20" customHeight="1" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="10" t="s">
+        <v>243</v>
+      </c>
+      <c r="B67" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="C67" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="D67" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="E67" s="10" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="68" ht="20" customHeight="1" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="10" t="s">
+        <v>244</v>
+      </c>
+      <c r="B68" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="C68" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="D68" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="E68" s="10" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="69" ht="20" customHeight="1" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="10" t="s">
+        <v>245</v>
+      </c>
+      <c r="B69" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="C69" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="D69" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="E69" s="10" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="70" ht="20" customHeight="1" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="10" t="s">
+        <v>246</v>
+      </c>
+      <c r="B70" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="C70" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="D70" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="E70" s="10" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="71" ht="20" customHeight="1" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="10" t="s">
+        <v>247</v>
+      </c>
+      <c r="B71" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="C71" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="D71" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="E71" s="10" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="72" ht="20" customHeight="1" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="10" t="s">
+        <v>248</v>
+      </c>
+      <c r="B72" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="C72" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="D72" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="E72" s="10" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="73" ht="20" customHeight="1" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="10" t="s">
+        <v>249</v>
+      </c>
+      <c r="B73" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="C73" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="D73" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="E73" s="10" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="74" ht="20" customHeight="1" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="10" t="s">
+        <v>250</v>
+      </c>
+      <c r="B74" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="C74" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="D74" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="E74" s="10" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="75" ht="20" customHeight="1" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="10" t="s">
+        <v>252</v>
+      </c>
+      <c r="B75" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="C75" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="D75" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="E75" s="10" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="76" ht="20" customHeight="1" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="10" t="s">
+        <v>253</v>
+      </c>
+      <c r="B76" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="C76" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="D76" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="E76" s="10" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="77" ht="20" customHeight="1" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="10" t="s">
+        <v>254</v>
+      </c>
+      <c r="B77" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="C77" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="D77" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="E77" s="10" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="78" ht="20" customHeight="1" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="10" t="s">
+        <v>255</v>
+      </c>
+      <c r="B78" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="C78" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="D78" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="E78" s="10" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="79" ht="20" customHeight="1" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="10" t="s">
+        <v>256</v>
+      </c>
+      <c r="B79" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="C79" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="D79" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="E79" s="10" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="80" ht="20" customHeight="1" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="10" t="s">
+        <v>257</v>
+      </c>
+      <c r="B80" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="C80" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="D80" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="E80" s="10" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="81" ht="20" customHeight="1" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="10" t="s">
+        <v>258</v>
+      </c>
+      <c r="B81" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="C81" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="D81" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="E81" s="10" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="82" ht="20" customHeight="1" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="10" t="s">
+        <v>259</v>
+      </c>
+      <c r="B82" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="C82" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="D82" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="E82" s="10" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="83" ht="20" customHeight="1" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A83" s="10" t="s">
+        <v>260</v>
+      </c>
+      <c r="B83" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="C83" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="D83" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="E83" s="10" t="s">
+        <v>181</v>
       </c>
     </row>
   </sheetData>
